--- a/artfynd/A 58951-2023 artfynd.xlsx
+++ b/artfynd/A 58951-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252846</v>
+        <v>121252843</v>
       </c>
       <c r="B2" t="n">
-        <v>79679</v>
+        <v>79683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445362</v>
+        <v>445361</v>
       </c>
       <c r="R2" t="n">
-        <v>7026548</v>
+        <v>7026537</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252843</v>
+        <v>121252844</v>
       </c>
       <c r="B3" t="n">
-        <v>79680</v>
+        <v>74692</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,25 +819,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445361</v>
+        <v>445362</v>
       </c>
       <c r="R3" t="n">
-        <v>7026537</v>
+        <v>7026548</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,7 +921,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252841</v>
+        <v>121252842</v>
       </c>
       <c r="B4" t="n">
-        <v>74710</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,21 +955,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445424</v>
+        <v>445361</v>
       </c>
       <c r="R4" t="n">
-        <v>7026577</v>
+        <v>7026537</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,17 +1043,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>På ved vid basen av granstubbe # Picea abies</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252848</v>
+        <v>121252841</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>74713</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445382</v>
+        <v>445424</v>
       </c>
       <c r="R5" t="n">
-        <v>7026578</v>
+        <v>7026577</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På ved vid basen av granstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252847</v>
+        <v>121252845</v>
       </c>
       <c r="B6" t="n">
-        <v>79679</v>
+        <v>79717</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445368</v>
+        <v>445362</v>
       </c>
       <c r="R6" t="n">
-        <v>7026552</v>
+        <v>7026548</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252845</v>
+        <v>121252848</v>
       </c>
       <c r="B7" t="n">
-        <v>79714</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,20 +1347,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445362</v>
+        <v>445382</v>
       </c>
       <c r="R7" t="n">
-        <v>7026548</v>
+        <v>7026578</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1439,17 +1439,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252842</v>
+        <v>121252846</v>
       </c>
       <c r="B8" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445361</v>
+        <v>445362</v>
       </c>
       <c r="R8" t="n">
-        <v>7026537</v>
+        <v>7026548</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252844</v>
+        <v>121252847</v>
       </c>
       <c r="B9" t="n">
-        <v>74689</v>
+        <v>79682</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1611,25 +1611,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445362</v>
+        <v>445368</v>
       </c>
       <c r="R9" t="n">
-        <v>7026548</v>
+        <v>7026552</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 58951-2023 artfynd.xlsx
+++ b/artfynd/A 58951-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252843</v>
+        <v>121252848</v>
       </c>
       <c r="B2" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445361</v>
+        <v>445382</v>
       </c>
       <c r="R2" t="n">
-        <v>7026537</v>
+        <v>7026578</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,17 +779,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252844</v>
+        <v>121252846</v>
       </c>
       <c r="B3" t="n">
-        <v>74692</v>
+        <v>79682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,25 +819,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252842</v>
+        <v>121252843</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>79683</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,21 +955,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252841</v>
+        <v>121252842</v>
       </c>
       <c r="B5" t="n">
-        <v>74713</v>
+        <v>79682</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445424</v>
+        <v>445361</v>
       </c>
       <c r="R5" t="n">
-        <v>7026577</v>
+        <v>7026537</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>På ved vid basen av granstubbe # Picea abies</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252848</v>
+        <v>121252847</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445382</v>
+        <v>445368</v>
       </c>
       <c r="R7" t="n">
-        <v>7026578</v>
+        <v>7026552</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1439,17 +1439,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252846</v>
+        <v>121252841</v>
       </c>
       <c r="B8" t="n">
-        <v>79682</v>
+        <v>74713</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1483,21 +1483,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445362</v>
+        <v>445424</v>
       </c>
       <c r="R8" t="n">
-        <v>7026548</v>
+        <v>7026577</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På ved vid basen av granstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252847</v>
+        <v>121252844</v>
       </c>
       <c r="B9" t="n">
-        <v>79682</v>
+        <v>74692</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1611,25 +1611,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445368</v>
+        <v>445362</v>
       </c>
       <c r="R9" t="n">
-        <v>7026552</v>
+        <v>7026548</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 58951-2023 artfynd.xlsx
+++ b/artfynd/A 58951-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252848</v>
+        <v>121252847</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445382</v>
+        <v>445368</v>
       </c>
       <c r="R2" t="n">
-        <v>7026578</v>
+        <v>7026552</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,17 +779,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252846</v>
+        <v>121252844</v>
       </c>
       <c r="B3" t="n">
-        <v>79682</v>
+        <v>74694</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,25 +819,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252843</v>
+        <v>121252846</v>
       </c>
       <c r="B4" t="n">
-        <v>79683</v>
+        <v>79685</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,21 +955,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445361</v>
+        <v>445362</v>
       </c>
       <c r="R4" t="n">
-        <v>7026537</v>
+        <v>7026548</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252842</v>
+        <v>121252841</v>
       </c>
       <c r="B5" t="n">
-        <v>79682</v>
+        <v>74715</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445361</v>
+        <v>445424</v>
       </c>
       <c r="R5" t="n">
-        <v>7026537</v>
+        <v>7026577</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På ved vid basen av granstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1206,7 +1206,7 @@
         <v>121252845</v>
       </c>
       <c r="B6" t="n">
-        <v>79717</v>
+        <v>79720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252847</v>
+        <v>121252843</v>
       </c>
       <c r="B7" t="n">
-        <v>79682</v>
+        <v>79686</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445368</v>
+        <v>445361</v>
       </c>
       <c r="R7" t="n">
-        <v>7026552</v>
+        <v>7026537</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252841</v>
+        <v>121252842</v>
       </c>
       <c r="B8" t="n">
-        <v>74713</v>
+        <v>79685</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1483,21 +1483,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445424</v>
+        <v>445361</v>
       </c>
       <c r="R8" t="n">
-        <v>7026577</v>
+        <v>7026537</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På ved vid basen av granstubbe # Picea abies</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252844</v>
+        <v>121252848</v>
       </c>
       <c r="B9" t="n">
-        <v>74692</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1611,25 +1611,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445362</v>
+        <v>445382</v>
       </c>
       <c r="R9" t="n">
-        <v>7026548</v>
+        <v>7026578</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1703,17 +1703,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 58951-2023 artfynd.xlsx
+++ b/artfynd/A 58951-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252847</v>
+        <v>121252844</v>
       </c>
       <c r="B2" t="n">
-        <v>79685</v>
+        <v>74694</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445368</v>
+        <v>445362</v>
       </c>
       <c r="R2" t="n">
-        <v>7026552</v>
+        <v>7026548</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252844</v>
+        <v>121252843</v>
       </c>
       <c r="B3" t="n">
-        <v>74694</v>
+        <v>79686</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,25 +819,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445362</v>
+        <v>445361</v>
       </c>
       <c r="R3" t="n">
-        <v>7026548</v>
+        <v>7026537</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,7 +921,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,7 +939,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252846</v>
+        <v>121252847</v>
       </c>
       <c r="B4" t="n">
         <v>79685</v>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445362</v>
+        <v>445368</v>
       </c>
       <c r="R4" t="n">
-        <v>7026548</v>
+        <v>7026552</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252841</v>
+        <v>121252845</v>
       </c>
       <c r="B5" t="n">
-        <v>74715</v>
+        <v>79720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,25 +1083,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1467</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445424</v>
+        <v>445362</v>
       </c>
       <c r="R5" t="n">
-        <v>7026577</v>
+        <v>7026548</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>På ved vid basen av granstubbe # Picea abies</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252845</v>
+        <v>121252842</v>
       </c>
       <c r="B6" t="n">
-        <v>79720</v>
+        <v>79685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,25 +1215,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445362</v>
+        <v>445361</v>
       </c>
       <c r="R6" t="n">
-        <v>7026548</v>
+        <v>7026537</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252843</v>
+        <v>121252841</v>
       </c>
       <c r="B7" t="n">
-        <v>79686</v>
+        <v>74715</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445361</v>
+        <v>445424</v>
       </c>
       <c r="R7" t="n">
-        <v>7026537</v>
+        <v>7026577</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1439,17 +1439,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På ved vid basen av granstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252842</v>
+        <v>121252846</v>
       </c>
       <c r="B8" t="n">
         <v>79685</v>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445361</v>
+        <v>445362</v>
       </c>
       <c r="R8" t="n">
-        <v>7026537</v>
+        <v>7026548</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 58951-2023 artfynd.xlsx
+++ b/artfynd/A 58951-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252844</v>
+        <v>121252845</v>
       </c>
       <c r="B2" t="n">
-        <v>74694</v>
+        <v>79723</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>6463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252843</v>
+        <v>121252842</v>
       </c>
       <c r="B3" t="n">
-        <v>79686</v>
+        <v>79688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,21 +823,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252847</v>
+        <v>121252848</v>
       </c>
       <c r="B4" t="n">
-        <v>79685</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,21 +955,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445368</v>
+        <v>445382</v>
       </c>
       <c r="R4" t="n">
-        <v>7026552</v>
+        <v>7026578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,17 +1043,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252845</v>
+        <v>121252844</v>
       </c>
       <c r="B5" t="n">
-        <v>79720</v>
+        <v>74697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1203,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252842</v>
+        <v>121252847</v>
       </c>
       <c r="B6" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445361</v>
+        <v>445368</v>
       </c>
       <c r="R6" t="n">
-        <v>7026537</v>
+        <v>7026552</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252841</v>
+        <v>121252843</v>
       </c>
       <c r="B7" t="n">
-        <v>74715</v>
+        <v>79689</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445424</v>
+        <v>445361</v>
       </c>
       <c r="R7" t="n">
-        <v>7026577</v>
+        <v>7026537</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1439,17 +1439,17 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På ved vid basen av granstubbe # Picea abies</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1470,7 +1470,7 @@
         <v>121252846</v>
       </c>
       <c r="B8" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252848</v>
+        <v>121252841</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>74718</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1615,21 +1615,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445382</v>
+        <v>445424</v>
       </c>
       <c r="R9" t="n">
-        <v>7026578</v>
+        <v>7026577</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På ved vid basen av granstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 58951-2023 artfynd.xlsx
+++ b/artfynd/A 58951-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252845</v>
+        <v>121252846</v>
       </c>
       <c r="B2" t="n">
-        <v>79723</v>
+        <v>79688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252842</v>
+        <v>121252848</v>
       </c>
       <c r="B3" t="n">
-        <v>79688</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,21 +823,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445361</v>
+        <v>445382</v>
       </c>
       <c r="R3" t="n">
-        <v>7026537</v>
+        <v>7026578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,17 +911,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252848</v>
+        <v>121252843</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>79689</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,21 +955,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445382</v>
+        <v>445361</v>
       </c>
       <c r="R4" t="n">
-        <v>7026578</v>
+        <v>7026537</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,17 +1043,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252844</v>
+        <v>121252845</v>
       </c>
       <c r="B5" t="n">
-        <v>74697</v>
+        <v>79723</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1335,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252843</v>
+        <v>121252844</v>
       </c>
       <c r="B7" t="n">
-        <v>79689</v>
+        <v>74697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,25 +1347,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445361</v>
+        <v>445362</v>
       </c>
       <c r="R7" t="n">
-        <v>7026537</v>
+        <v>7026548</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252846</v>
+        <v>121252842</v>
       </c>
       <c r="B8" t="n">
         <v>79688</v>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445362</v>
+        <v>445361</v>
       </c>
       <c r="R8" t="n">
-        <v>7026548</v>
+        <v>7026537</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 58951-2023 artfynd.xlsx
+++ b/artfynd/A 58951-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121252846</v>
       </c>
       <c r="B2" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252848</v>
+        <v>121252844</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
+        <v>74698</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,25 +819,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445382</v>
+        <v>445362</v>
       </c>
       <c r="R3" t="n">
-        <v>7026578</v>
+        <v>7026548</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,17 +911,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,7 +939,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252843</v>
+        <v>121252842</v>
       </c>
       <c r="B4" t="n">
         <v>79689</v>
@@ -955,21 +955,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1071,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252845</v>
+        <v>121252848</v>
       </c>
       <c r="B5" t="n">
-        <v>79723</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,20 +1083,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445362</v>
+        <v>445382</v>
       </c>
       <c r="R5" t="n">
-        <v>7026548</v>
+        <v>7026578</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252847</v>
+        <v>121252843</v>
       </c>
       <c r="B6" t="n">
-        <v>79688</v>
+        <v>79690</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1219,21 +1219,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445368</v>
+        <v>445361</v>
       </c>
       <c r="R6" t="n">
-        <v>7026552</v>
+        <v>7026537</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252844</v>
+        <v>121252847</v>
       </c>
       <c r="B7" t="n">
-        <v>74697</v>
+        <v>79689</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,25 +1347,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445362</v>
+        <v>445368</v>
       </c>
       <c r="R7" t="n">
-        <v>7026548</v>
+        <v>7026552</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252842</v>
+        <v>121252845</v>
       </c>
       <c r="B8" t="n">
-        <v>79688</v>
+        <v>79724</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1479,25 +1479,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445361</v>
+        <v>445362</v>
       </c>
       <c r="R8" t="n">
-        <v>7026537</v>
+        <v>7026548</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1602,7 +1602,7 @@
         <v>121252841</v>
       </c>
       <c r="B9" t="n">
-        <v>74718</v>
+        <v>74719</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 58951-2023 artfynd.xlsx
+++ b/artfynd/A 58951-2023 artfynd.xlsx
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252845</v>
+        <v>121252841</v>
       </c>
       <c r="B8" t="n">
-        <v>79724</v>
+        <v>74719</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1479,25 +1479,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6463</v>
+        <v>1467</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445362</v>
+        <v>445424</v>
       </c>
       <c r="R8" t="n">
-        <v>7026548</v>
+        <v>7026577</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På ved vid basen av granstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252841</v>
+        <v>121252845</v>
       </c>
       <c r="B9" t="n">
-        <v>74719</v>
+        <v>79724</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1611,25 +1611,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445424</v>
+        <v>445362</v>
       </c>
       <c r="R9" t="n">
-        <v>7026577</v>
+        <v>7026548</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1703,17 +1703,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På ved vid basen av granstubbe # Picea abies</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 58951-2023 artfynd.xlsx
+++ b/artfynd/A 58951-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121252846</v>
       </c>
       <c r="B2" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252844</v>
+        <v>121252847</v>
       </c>
       <c r="B3" t="n">
-        <v>74698</v>
+        <v>79690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,25 +819,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445362</v>
+        <v>445368</v>
       </c>
       <c r="R3" t="n">
-        <v>7026548</v>
+        <v>7026552</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,7 +921,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252842</v>
+        <v>121252841</v>
       </c>
       <c r="B4" t="n">
-        <v>79689</v>
+        <v>74720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,21 +955,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445361</v>
+        <v>445424</v>
       </c>
       <c r="R4" t="n">
-        <v>7026537</v>
+        <v>7026577</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,17 +1043,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På ved vid basen av granstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252848</v>
+        <v>121252842</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445382</v>
+        <v>445361</v>
       </c>
       <c r="R5" t="n">
-        <v>7026578</v>
+        <v>7026537</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252843</v>
+        <v>121252848</v>
       </c>
       <c r="B6" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1219,21 +1219,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445361</v>
+        <v>445382</v>
       </c>
       <c r="R6" t="n">
-        <v>7026537</v>
+        <v>7026578</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252847</v>
+        <v>121252844</v>
       </c>
       <c r="B7" t="n">
-        <v>79689</v>
+        <v>74699</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,25 +1347,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445368</v>
+        <v>445362</v>
       </c>
       <c r="R7" t="n">
-        <v>7026552</v>
+        <v>7026548</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252841</v>
+        <v>121252843</v>
       </c>
       <c r="B8" t="n">
-        <v>74719</v>
+        <v>79691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1483,21 +1483,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445424</v>
+        <v>445361</v>
       </c>
       <c r="R8" t="n">
-        <v>7026577</v>
+        <v>7026537</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På ved vid basen av granstubbe # Picea abies</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1602,7 +1602,7 @@
         <v>121252845</v>
       </c>
       <c r="B9" t="n">
-        <v>79724</v>
+        <v>79725</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 58951-2023 artfynd.xlsx
+++ b/artfynd/A 58951-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252846</v>
+        <v>121252843</v>
       </c>
       <c r="B2" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445362</v>
+        <v>445361</v>
       </c>
       <c r="R2" t="n">
-        <v>7026548</v>
+        <v>7026537</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,7 +807,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252847</v>
+        <v>121252846</v>
       </c>
       <c r="B3" t="n">
         <v>79690</v>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445368</v>
+        <v>445362</v>
       </c>
       <c r="R3" t="n">
-        <v>7026552</v>
+        <v>7026548</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,7 +921,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252841</v>
+        <v>121252842</v>
       </c>
       <c r="B4" t="n">
-        <v>74720</v>
+        <v>79690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,21 +955,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445424</v>
+        <v>445361</v>
       </c>
       <c r="R4" t="n">
-        <v>7026577</v>
+        <v>7026537</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,17 +1043,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>På ved vid basen av granstubbe # Picea abies</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252842</v>
+        <v>121252844</v>
       </c>
       <c r="B5" t="n">
-        <v>79690</v>
+        <v>74699</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,25 +1083,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445361</v>
+        <v>445362</v>
       </c>
       <c r="R5" t="n">
-        <v>7026537</v>
+        <v>7026548</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252848</v>
+        <v>121252841</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>74720</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1219,21 +1219,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445382</v>
+        <v>445424</v>
       </c>
       <c r="R6" t="n">
-        <v>7026578</v>
+        <v>7026577</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På ved vid basen av granstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252844</v>
+        <v>121252845</v>
       </c>
       <c r="B7" t="n">
-        <v>74699</v>
+        <v>79725</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252843</v>
+        <v>121252848</v>
       </c>
       <c r="B8" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1483,21 +1483,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445361</v>
+        <v>445382</v>
       </c>
       <c r="R8" t="n">
-        <v>7026537</v>
+        <v>7026578</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252845</v>
+        <v>121252847</v>
       </c>
       <c r="B9" t="n">
-        <v>79725</v>
+        <v>79690</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1611,25 +1611,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445362</v>
+        <v>445368</v>
       </c>
       <c r="R9" t="n">
-        <v>7026548</v>
+        <v>7026552</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 58951-2023 artfynd.xlsx
+++ b/artfynd/A 58951-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252843</v>
+        <v>121252841</v>
       </c>
       <c r="B2" t="n">
-        <v>79691</v>
+        <v>74720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445361</v>
+        <v>445424</v>
       </c>
       <c r="R2" t="n">
-        <v>7026537</v>
+        <v>7026577</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,17 +779,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På ved vid basen av granstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252846</v>
+        <v>121252848</v>
       </c>
       <c r="B3" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,21 +823,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445362</v>
+        <v>445382</v>
       </c>
       <c r="R3" t="n">
-        <v>7026548</v>
+        <v>7026578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,17 +911,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252844</v>
+        <v>121252847</v>
       </c>
       <c r="B5" t="n">
-        <v>74699</v>
+        <v>79690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1083,25 +1083,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445362</v>
+        <v>445368</v>
       </c>
       <c r="R5" t="n">
-        <v>7026548</v>
+        <v>7026552</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252841</v>
+        <v>121252843</v>
       </c>
       <c r="B6" t="n">
-        <v>74720</v>
+        <v>79691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1219,21 +1219,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1467</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445424</v>
+        <v>445361</v>
       </c>
       <c r="R6" t="n">
-        <v>7026577</v>
+        <v>7026537</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På ved vid basen av granstubbe # Picea abies</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252845</v>
+        <v>121252844</v>
       </c>
       <c r="B7" t="n">
-        <v>79725</v>
+        <v>74699</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6439</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252848</v>
+        <v>121252846</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1483,21 +1483,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445382</v>
+        <v>445362</v>
       </c>
       <c r="R8" t="n">
-        <v>7026578</v>
+        <v>7026548</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252847</v>
+        <v>121252845</v>
       </c>
       <c r="B9" t="n">
-        <v>79690</v>
+        <v>79725</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1611,25 +1611,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445368</v>
+        <v>445362</v>
       </c>
       <c r="R9" t="n">
-        <v>7026552</v>
+        <v>7026548</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 58951-2023 artfynd.xlsx
+++ b/artfynd/A 58951-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252841</v>
+        <v>121252847</v>
       </c>
       <c r="B2" t="n">
-        <v>74720</v>
+        <v>79690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445424</v>
+        <v>445368</v>
       </c>
       <c r="R2" t="n">
-        <v>7026577</v>
+        <v>7026552</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,17 +779,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>På ved vid basen av granstubbe # Picea abies</t>
+          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252848</v>
+        <v>121252845</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>79725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,20 +819,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445382</v>
+        <v>445362</v>
       </c>
       <c r="R3" t="n">
-        <v>7026578</v>
+        <v>7026548</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,17 +911,17 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252842</v>
+        <v>121252844</v>
       </c>
       <c r="B4" t="n">
-        <v>79690</v>
+        <v>74699</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,25 +951,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445361</v>
+        <v>445362</v>
       </c>
       <c r="R4" t="n">
-        <v>7026537</v>
+        <v>7026548</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252847</v>
+        <v>121252843</v>
       </c>
       <c r="B5" t="n">
-        <v>79690</v>
+        <v>79691</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445368</v>
+        <v>445361</v>
       </c>
       <c r="R5" t="n">
-        <v>7026552</v>
+        <v>7026537</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252843</v>
+        <v>121252848</v>
       </c>
       <c r="B6" t="n">
-        <v>79691</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1219,21 +1219,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445361</v>
+        <v>445382</v>
       </c>
       <c r="R6" t="n">
-        <v>7026537</v>
+        <v>7026578</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121252844</v>
+        <v>121252846</v>
       </c>
       <c r="B7" t="n">
-        <v>74699</v>
+        <v>79690</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,25 +1347,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1467,7 +1467,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252846</v>
+        <v>121252842</v>
       </c>
       <c r="B8" t="n">
         <v>79690</v>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445362</v>
+        <v>445361</v>
       </c>
       <c r="R8" t="n">
-        <v>7026548</v>
+        <v>7026537</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252845</v>
+        <v>121252841</v>
       </c>
       <c r="B9" t="n">
-        <v>79725</v>
+        <v>74720</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1611,25 +1611,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445362</v>
+        <v>445424</v>
       </c>
       <c r="R9" t="n">
-        <v>7026548</v>
+        <v>7026577</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1703,17 +1703,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På ved vid basen av granstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 58951-2023 artfynd.xlsx
+++ b/artfynd/A 58951-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121252847</v>
+        <v>121252841</v>
       </c>
       <c r="B2" t="n">
-        <v>79690</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445368</v>
+        <v>445424</v>
       </c>
       <c r="R2" t="n">
-        <v>7026552</v>
+        <v>7026577</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,17 +774,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
+          <t>På ved vid basen av granstubbe # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,37 +802,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121252845</v>
+        <v>121252843</v>
       </c>
       <c r="B3" t="n">
-        <v>79725</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445362</v>
+        <v>445361</v>
       </c>
       <c r="R3" t="n">
-        <v>7026548</v>
+        <v>7026537</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,7 +911,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,37 +929,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121252844</v>
+        <v>121252848</v>
       </c>
       <c r="B4" t="n">
-        <v>74699</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445362</v>
+        <v>445382</v>
       </c>
       <c r="R4" t="n">
-        <v>7026548</v>
+        <v>7026578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,17 +1028,17 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,37 +1056,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121252843</v>
+        <v>121252844</v>
       </c>
       <c r="B5" t="n">
-        <v>79691</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1111,10 +1091,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445361</v>
+        <v>445362</v>
       </c>
       <c r="R5" t="n">
-        <v>7026537</v>
+        <v>7026548</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1156,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,7 +1165,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,15 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121252848</v>
+        <v>121252842</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,21 +1194,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1243,10 +1218,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445382</v>
+        <v>445361</v>
       </c>
       <c r="R6" t="n">
-        <v>7026578</v>
+        <v>7026537</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1278,7 +1253,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1288,7 +1263,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,17 +1282,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1338,12 +1313,7 @@
         <v>121252846</v>
       </c>
       <c r="B7" t="n">
-        <v>79690</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1467,15 +1437,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121252842</v>
+        <v>121252847</v>
       </c>
       <c r="B8" t="n">
-        <v>79690</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,10 +1472,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445361</v>
+        <v>445368</v>
       </c>
       <c r="R8" t="n">
-        <v>7026537</v>
+        <v>7026552</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1507,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1517,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,7 +1546,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande sälg (45 cm dbh) # Salix caprea</t>
+          <t>På bark på stam av levande sälg (27 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1599,37 +1564,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121252841</v>
+        <v>121252845</v>
       </c>
       <c r="B9" t="n">
-        <v>74720</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1639,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445424</v>
+        <v>445362</v>
       </c>
       <c r="R9" t="n">
-        <v>7026577</v>
+        <v>7026548</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1634,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1684,7 +1644,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1703,17 +1663,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På ved vid basen av granstubbe # Picea abies</t>
+          <t>På bark på stam av levande sälg (65 cm dbh) # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 58951-2023 artfynd.xlsx
+++ b/artfynd/A 58951-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252841</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,6 +936,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252843</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1053,6 +1068,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252848</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1180,6 +1200,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252844</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1307,6 +1332,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252842</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1434,6 +1464,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252846</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1561,6 +1596,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252847</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1688,8 +1728,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121252845</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>